--- a/artfynd/A 61173-2025 artfynd.xlsx
+++ b/artfynd/A 61173-2025 artfynd.xlsx
@@ -782,45 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130733307</v>
+        <v>130746925</v>
       </c>
       <c r="B3" t="n">
-        <v>80316</v>
+        <v>92488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tavåsänget, Tavåsänget, Jmt</t>
+          <t>Taåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500644</v>
+        <v>500725</v>
       </c>
       <c r="R3" t="n">
-        <v>6957731</v>
+        <v>6957686</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,32 +853,18 @@
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På Björk</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -894,48 +883,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130746925</v>
+        <v>130733307</v>
       </c>
       <c r="B4" t="n">
-        <v>92488</v>
+        <v>80316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Taåsänget, Jmt</t>
+          <t>Tavåsänget, Tavåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500725</v>
+        <v>500644</v>
       </c>
       <c r="R4" t="n">
-        <v>6957686</v>
+        <v>6957731</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,18 +951,32 @@
           <t>2026-01-17</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På Björk</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130735839</v>
+        <v>130732414</v>
       </c>
       <c r="B8" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,37 +1327,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rörmyren, Rörmyren, Jmt</t>
+          <t>Tavåsänget, Tavåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500636</v>
+        <v>500471</v>
       </c>
       <c r="R8" t="n">
-        <v>6957463</v>
+        <v>6957746</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130732414</v>
+        <v>130735839</v>
       </c>
       <c r="B9" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,37 +1434,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tavåsänget, Tavåsänget, Jmt</t>
+          <t>Rörmyren, Rörmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500471</v>
+        <v>500636</v>
       </c>
       <c r="R9" t="n">
-        <v>6957746</v>
+        <v>6957463</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 61173-2025 artfynd.xlsx
+++ b/artfynd/A 61173-2025 artfynd.xlsx
@@ -782,48 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130746925</v>
+        <v>130733307</v>
       </c>
       <c r="B3" t="n">
-        <v>92488</v>
+        <v>80316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Taåsänget, Jmt</t>
+          <t>Tavåsänget, Tavåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500725</v>
+        <v>500644</v>
       </c>
       <c r="R3" t="n">
-        <v>6957686</v>
+        <v>6957731</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,18 +850,32 @@
           <t>2026-01-17</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På Björk</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -883,45 +894,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130733307</v>
+        <v>130746925</v>
       </c>
       <c r="B4" t="n">
-        <v>80316</v>
+        <v>92488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tavåsänget, Tavåsänget, Jmt</t>
+          <t>Taåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500644</v>
+        <v>500725</v>
       </c>
       <c r="R4" t="n">
-        <v>6957731</v>
+        <v>6957686</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -951,32 +965,18 @@
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På Björk</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130732952</v>
+        <v>130733209</v>
       </c>
       <c r="B5" t="n">
-        <v>79801</v>
+        <v>80316</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500524</v>
+        <v>500622</v>
       </c>
       <c r="R5" t="n">
-        <v>6957781</v>
+        <v>6957749</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130733209</v>
+        <v>130732952</v>
       </c>
       <c r="B6" t="n">
-        <v>80316</v>
+        <v>79801</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500622</v>
+        <v>500524</v>
       </c>
       <c r="R6" t="n">
-        <v>6957749</v>
+        <v>6957781</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 61173-2025 artfynd.xlsx
+++ b/artfynd/A 61173-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130736086</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,45 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130733307</v>
+        <v>130746925</v>
       </c>
       <c r="B3" t="n">
-        <v>80316</v>
+        <v>92501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tavåsänget, Tavåsänget, Jmt</t>
+          <t>Taåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500644</v>
+        <v>500725</v>
       </c>
       <c r="R3" t="n">
-        <v>6957731</v>
+        <v>6957686</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,32 +853,18 @@
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På Björk</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -894,48 +883,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130746925</v>
+        <v>130733307</v>
       </c>
       <c r="B4" t="n">
-        <v>92488</v>
+        <v>80324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Taåsänget, Jmt</t>
+          <t>Tavåsänget, Tavåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500725</v>
+        <v>500644</v>
       </c>
       <c r="R4" t="n">
-        <v>6957686</v>
+        <v>6957731</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,18 +951,32 @@
           <t>2026-01-17</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På Björk</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130733209</v>
+        <v>130732952</v>
       </c>
       <c r="B5" t="n">
-        <v>80316</v>
+        <v>79809</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500622</v>
+        <v>500524</v>
       </c>
       <c r="R5" t="n">
-        <v>6957749</v>
+        <v>6957781</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130732952</v>
+        <v>130733209</v>
       </c>
       <c r="B6" t="n">
-        <v>79801</v>
+        <v>80324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500524</v>
+        <v>500622</v>
       </c>
       <c r="R6" t="n">
-        <v>6957781</v>
+        <v>6957749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,48 +1209,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130735830</v>
+        <v>130732414</v>
       </c>
       <c r="B7" t="n">
-        <v>92360</v>
+        <v>79219</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rörmyren, Rörmyren, Jmt</t>
+          <t>Tavåsänget, Tavåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500636</v>
+        <v>500471</v>
       </c>
       <c r="R7" t="n">
-        <v>6957463</v>
+        <v>6957746</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130732414</v>
+        <v>130735839</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>80324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,37 +1327,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tavåsänget, Tavåsänget, Jmt</t>
+          <t>Rörmyren, Rörmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500471</v>
+        <v>500636</v>
       </c>
       <c r="R8" t="n">
-        <v>6957746</v>
+        <v>6957463</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,32 +1423,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130735839</v>
+        <v>130735830</v>
       </c>
       <c r="B9" t="n">
-        <v>80316</v>
+        <v>92373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,7 +1533,7 @@
         <v>130733442</v>
       </c>
       <c r="B10" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>130733969</v>
       </c>
       <c r="B11" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>130732790</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>130736016</v>
       </c>
       <c r="B13" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>130735568</v>
       </c>
       <c r="B14" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>130734065</v>
       </c>
       <c r="B15" t="n">
-        <v>92488</v>
+        <v>92501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>130735950</v>
       </c>
       <c r="B16" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>130732978</v>
       </c>
       <c r="B17" t="n">
-        <v>78218</v>
+        <v>78226</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 61173-2025 artfynd.xlsx
+++ b/artfynd/A 61173-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130736086</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,48 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130746925</v>
+        <v>130733307</v>
       </c>
       <c r="B3" t="n">
-        <v>92501</v>
+        <v>80325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Taåsänget, Jmt</t>
+          <t>Tavåsänget, Tavåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500725</v>
+        <v>500644</v>
       </c>
       <c r="R3" t="n">
-        <v>6957686</v>
+        <v>6957731</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,18 +850,32 @@
           <t>2026-01-17</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På Björk</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -883,45 +894,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130733307</v>
+        <v>130746925</v>
       </c>
       <c r="B4" t="n">
-        <v>80324</v>
+        <v>92502</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tavåsänget, Tavåsänget, Jmt</t>
+          <t>Taåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500644</v>
+        <v>500725</v>
       </c>
       <c r="R4" t="n">
-        <v>6957731</v>
+        <v>6957686</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -951,32 +965,18 @@
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På Björk</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130732952</v>
+        <v>130733209</v>
       </c>
       <c r="B5" t="n">
-        <v>79809</v>
+        <v>80325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500524</v>
+        <v>500622</v>
       </c>
       <c r="R5" t="n">
-        <v>6957781</v>
+        <v>6957749</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130733209</v>
+        <v>130732952</v>
       </c>
       <c r="B6" t="n">
-        <v>80324</v>
+        <v>79810</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500622</v>
+        <v>500524</v>
       </c>
       <c r="R6" t="n">
-        <v>6957749</v>
+        <v>6957781</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,7 +1212,7 @@
         <v>130732414</v>
       </c>
       <c r="B7" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>130735839</v>
       </c>
       <c r="B8" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>130735830</v>
       </c>
       <c r="B9" t="n">
-        <v>92373</v>
+        <v>92374</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>130733442</v>
       </c>
       <c r="B10" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>130733969</v>
       </c>
       <c r="B11" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>130732790</v>
       </c>
       <c r="B12" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>130736016</v>
       </c>
       <c r="B13" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>130735568</v>
       </c>
       <c r="B14" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>130734065</v>
       </c>
       <c r="B15" t="n">
-        <v>92501</v>
+        <v>92502</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>130735950</v>
       </c>
       <c r="B16" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>130732978</v>
       </c>
       <c r="B17" t="n">
-        <v>78226</v>
+        <v>78227</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 61173-2025 artfynd.xlsx
+++ b/artfynd/A 61173-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130736086</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,45 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130733307</v>
+        <v>130746925</v>
       </c>
       <c r="B3" t="n">
-        <v>80325</v>
+        <v>92503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tavåsänget, Tavåsänget, Jmt</t>
+          <t>Taåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500644</v>
+        <v>500725</v>
       </c>
       <c r="R3" t="n">
-        <v>6957731</v>
+        <v>6957686</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,32 +853,18 @@
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På Björk</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -894,48 +883,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130746925</v>
+        <v>130733307</v>
       </c>
       <c r="B4" t="n">
-        <v>92502</v>
+        <v>80326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Taåsänget, Jmt</t>
+          <t>Tavåsänget, Tavåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500725</v>
+        <v>500644</v>
       </c>
       <c r="R4" t="n">
-        <v>6957686</v>
+        <v>6957731</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,18 +951,32 @@
           <t>2026-01-17</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På Björk</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -998,7 +998,7 @@
         <v>130733209</v>
       </c>
       <c r="B5" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>130732952</v>
       </c>
       <c r="B6" t="n">
-        <v>79810</v>
+        <v>79811</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,48 +1209,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130732414</v>
+        <v>130735830</v>
       </c>
       <c r="B7" t="n">
-        <v>79220</v>
+        <v>92375</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tavåsänget, Tavåsänget, Jmt</t>
+          <t>Rörmyren, Rörmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500471</v>
+        <v>500636</v>
       </c>
       <c r="R7" t="n">
-        <v>6957746</v>
+        <v>6957463</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130735839</v>
+        <v>130732414</v>
       </c>
       <c r="B8" t="n">
-        <v>80325</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,37 +1327,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rörmyren, Rörmyren, Jmt</t>
+          <t>Tavåsänget, Tavåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500636</v>
+        <v>500471</v>
       </c>
       <c r="R8" t="n">
-        <v>6957463</v>
+        <v>6957746</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,32 +1423,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130735830</v>
+        <v>130735839</v>
       </c>
       <c r="B9" t="n">
-        <v>92374</v>
+        <v>80326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,7 +1533,7 @@
         <v>130733442</v>
       </c>
       <c r="B10" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>130733969</v>
       </c>
       <c r="B11" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>130732790</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>130736016</v>
       </c>
       <c r="B13" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>130735568</v>
       </c>
       <c r="B14" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>130734065</v>
       </c>
       <c r="B15" t="n">
-        <v>92502</v>
+        <v>92503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>130735950</v>
       </c>
       <c r="B16" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>130732978</v>
       </c>
       <c r="B17" t="n">
-        <v>78227</v>
+        <v>78228</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 61173-2025 artfynd.xlsx
+++ b/artfynd/A 61173-2025 artfynd.xlsx
@@ -782,48 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130746925</v>
+        <v>130733307</v>
       </c>
       <c r="B3" t="n">
-        <v>92503</v>
+        <v>80326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Taåsänget, Jmt</t>
+          <t>Tavåsänget, Tavåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500725</v>
+        <v>500644</v>
       </c>
       <c r="R3" t="n">
-        <v>6957686</v>
+        <v>6957731</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,18 +850,32 @@
           <t>2026-01-17</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På Björk</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -883,45 +894,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130733307</v>
+        <v>130746925</v>
       </c>
       <c r="B4" t="n">
-        <v>80326</v>
+        <v>92503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tavåsänget, Tavåsänget, Jmt</t>
+          <t>Taåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500644</v>
+        <v>500725</v>
       </c>
       <c r="R4" t="n">
-        <v>6957731</v>
+        <v>6957686</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -951,32 +965,18 @@
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På Björk</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1209,48 +1209,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130735830</v>
+        <v>130732414</v>
       </c>
       <c r="B7" t="n">
-        <v>92375</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rörmyren, Rörmyren, Jmt</t>
+          <t>Tavåsänget, Tavåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500636</v>
+        <v>500471</v>
       </c>
       <c r="R7" t="n">
-        <v>6957463</v>
+        <v>6957746</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130732414</v>
+        <v>130735839</v>
       </c>
       <c r="B8" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,37 +1327,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tavåsänget, Tavåsänget, Jmt</t>
+          <t>Rörmyren, Rörmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500471</v>
+        <v>500636</v>
       </c>
       <c r="R8" t="n">
-        <v>6957746</v>
+        <v>6957463</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,32 +1423,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130735839</v>
+        <v>130735830</v>
       </c>
       <c r="B9" t="n">
-        <v>80326</v>
+        <v>92375</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 61173-2025 artfynd.xlsx
+++ b/artfynd/A 61173-2025 artfynd.xlsx
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130733209</v>
+        <v>130732952</v>
       </c>
       <c r="B5" t="n">
-        <v>80326</v>
+        <v>79811</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500622</v>
+        <v>500524</v>
       </c>
       <c r="R5" t="n">
-        <v>6957749</v>
+        <v>6957781</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130732952</v>
+        <v>130733209</v>
       </c>
       <c r="B6" t="n">
-        <v>79811</v>
+        <v>80326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500524</v>
+        <v>500622</v>
       </c>
       <c r="R6" t="n">
-        <v>6957781</v>
+        <v>6957749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 61173-2025 artfynd.xlsx
+++ b/artfynd/A 61173-2025 artfynd.xlsx
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130732952</v>
+        <v>130733209</v>
       </c>
       <c r="B5" t="n">
-        <v>79811</v>
+        <v>80326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500524</v>
+        <v>500622</v>
       </c>
       <c r="R5" t="n">
-        <v>6957781</v>
+        <v>6957749</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130733209</v>
+        <v>130732952</v>
       </c>
       <c r="B6" t="n">
-        <v>80326</v>
+        <v>79811</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500622</v>
+        <v>500524</v>
       </c>
       <c r="R6" t="n">
-        <v>6957749</v>
+        <v>6957781</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 61173-2025 artfynd.xlsx
+++ b/artfynd/A 61173-2025 artfynd.xlsx
@@ -782,45 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130733307</v>
+        <v>130746925</v>
       </c>
       <c r="B3" t="n">
-        <v>80326</v>
+        <v>92503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tavåsänget, Tavåsänget, Jmt</t>
+          <t>Taåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500644</v>
+        <v>500725</v>
       </c>
       <c r="R3" t="n">
-        <v>6957731</v>
+        <v>6957686</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,32 +853,18 @@
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På Björk</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -894,48 +883,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130746925</v>
+        <v>130733307</v>
       </c>
       <c r="B4" t="n">
-        <v>92503</v>
+        <v>80326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Taåsänget, Jmt</t>
+          <t>Tavåsänget, Tavåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500725</v>
+        <v>500644</v>
       </c>
       <c r="R4" t="n">
-        <v>6957686</v>
+        <v>6957731</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,18 +951,32 @@
           <t>2026-01-17</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På Björk</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61173-2025 artfynd.xlsx
+++ b/artfynd/A 61173-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130736086</v>
+        <v>130734065</v>
       </c>
       <c r="B2" t="n">
-        <v>79243</v>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500578</v>
+        <v>500759</v>
       </c>
       <c r="R2" t="n">
-        <v>6957637</v>
+        <v>6957667</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
         <v>130746925</v>
       </c>
       <c r="B3" t="n">
-        <v>92535</v>
+        <v>92637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,48 +883,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130733307</v>
+        <v>130735830</v>
       </c>
       <c r="B4" t="n">
-        <v>80348</v>
+        <v>92509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tavåsänget, Tavåsänget, Jmt</t>
+          <t>Rörmyren, Rörmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500644</v>
+        <v>500636</v>
       </c>
       <c r="R4" t="n">
-        <v>6957731</v>
+        <v>6957463</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -963,12 +963,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På Björk</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,32 +990,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130733209</v>
+        <v>130732414</v>
       </c>
       <c r="B5" t="n">
-        <v>80348</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500622</v>
+        <v>500471</v>
       </c>
       <c r="R5" t="n">
-        <v>6957749</v>
+        <v>6957746</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,7 +1060,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1075,7 +1070,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,32 +1097,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130732952</v>
+        <v>130736086</v>
       </c>
       <c r="B6" t="n">
-        <v>79833</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500524</v>
+        <v>500578</v>
       </c>
       <c r="R6" t="n">
-        <v>6957781</v>
+        <v>6957637</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,7 +1167,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1182,7 +1177,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130732414</v>
+        <v>130732790</v>
       </c>
       <c r="B7" t="n">
-        <v>79243</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,21 +1215,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1244,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500471</v>
+        <v>500566</v>
       </c>
       <c r="R7" t="n">
-        <v>6957746</v>
+        <v>6957735</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,7 +1274,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1289,7 +1284,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130735839</v>
+        <v>130733209</v>
       </c>
       <c r="B8" t="n">
-        <v>80348</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,17 +1342,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rörmyren, Rörmyren, Jmt</t>
+          <t>Tavåsänget, Tavåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500636</v>
+        <v>500622</v>
       </c>
       <c r="R8" t="n">
-        <v>6957463</v>
+        <v>6957749</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,7 +1381,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1396,7 +1391,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,48 +1418,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130735830</v>
+        <v>130733307</v>
       </c>
       <c r="B9" t="n">
-        <v>92407</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rörmyren, Rörmyren, Jmt</t>
+          <t>Tavåsänget, Tavåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500636</v>
+        <v>500644</v>
       </c>
       <c r="R9" t="n">
-        <v>6957463</v>
+        <v>6957731</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1493,7 +1488,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1503,7 +1498,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På Björk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,7 +1533,7 @@
         <v>130733442</v>
       </c>
       <c r="B10" t="n">
-        <v>80348</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>130733969</v>
       </c>
       <c r="B11" t="n">
-        <v>80348</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130732790</v>
+        <v>130735839</v>
       </c>
       <c r="B12" t="n">
-        <v>79000</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,37 +1755,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tavåsänget, Tavåsänget, Jmt</t>
+          <t>Rörmyren, Rörmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500566</v>
+        <v>500636</v>
       </c>
       <c r="R12" t="n">
-        <v>6957735</v>
+        <v>6957463</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130736016</v>
+        <v>130735950</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,39 +1862,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tavåsänget, Tavåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500595</v>
+        <v>500590</v>
       </c>
       <c r="R13" t="n">
-        <v>6957568</v>
+        <v>6957562</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1926,7 +1921,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1936,12 +1931,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1968,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130735568</v>
+        <v>130732978</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>78334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,42 +1969,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rörmyren, Rörmyren, Jmt</t>
+          <t>Tavåsänget, Tavåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500759</v>
+        <v>500524</v>
       </c>
       <c r="R14" t="n">
-        <v>6957405</v>
+        <v>6957781</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2043,7 +2028,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2053,12 +2038,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2085,45 +2065,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130734065</v>
+        <v>130735568</v>
       </c>
       <c r="B15" t="n">
-        <v>92535</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tavåsänget, Tavåsänget, Jmt</t>
+          <t>Rörmyren, Rörmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
         <v>500759</v>
       </c>
       <c r="R15" t="n">
-        <v>6957667</v>
+        <v>6957405</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2155,7 +2140,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2165,7 +2150,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2192,10 +2182,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130735950</v>
+        <v>130736016</v>
       </c>
       <c r="B16" t="n">
-        <v>80348</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,34 +2193,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tavåsänget, Tavåsänget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500590</v>
+        <v>500595</v>
       </c>
       <c r="R16" t="n">
-        <v>6957562</v>
+        <v>6957568</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2262,7 +2257,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2272,7 +2267,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2299,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130732978</v>
+        <v>130732952</v>
       </c>
       <c r="B17" t="n">
-        <v>78250</v>
+        <v>79917</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2310,21 +2310,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 61173-2025 artfynd.xlsx
+++ b/artfynd/A 61173-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734065</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746925</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130735830</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130732414</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130736086</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130732790</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,6 +1450,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130733209</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1527,6 +1567,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130733307</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1634,6 +1679,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130733442</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1741,6 +1791,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130733969</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1848,6 +1903,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130735839</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1955,6 +2015,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130735950</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2062,6 +2127,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130732978</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2179,6 +2249,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130735568</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2296,6 +2371,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130736016</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2403,8 +2483,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130732952</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>